--- a/data/trans_camb/IP21B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,6</t>
+          <t>0,0; 76,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,58</t>
+          <t>0,0; 71,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,12</t>
+          <t>0,0; 65,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,23</t>
+          <t>0,0; 65,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 43,09</t>
+          <t>-23,76; 42,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,37 +903,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 88,37</t>
+          <t>-23,62; 88,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 40,11</t>
+          <t>-27,86; 40,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 0,0</t>
+          <t>-50,77; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 0,0</t>
+          <t>-50,96; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 29,64</t>
+          <t>-17,96; 30,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 24,81</t>
+          <t>-23,32; 28,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 56,24</t>
+          <t>-18,85; 55,76</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,25; 71,22</t>
+          <t>-43,24; 85,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-71,26; 0,0</t>
+          <t>-71,48; 0,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-44,47; 0,0</t>
+          <t>-45,51; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 54,03</t>
+          <t>-22,39; 59,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 60,88</t>
+          <t>-22,17; 64,22</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 77,11</t>
+          <t>-47,87; 80,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 75,99</t>
+          <t>-47,87; 75,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,32</t>
+          <t>0,0; 67,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 56,73</t>
+          <t>-15,56; 52,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 70,22</t>
+          <t>-8,87; 66,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 0,0</t>
+          <t>-37,42; 0,0</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 74,18</t>
+          <t>-53,38; 73,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 55,12</t>
+          <t>-52,21; 43,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,35</t>
+          <t>0,0; 52,77</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,49</t>
+          <t>0,0; 53,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1988,32 +1988,32 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 44,1</t>
+          <t>-27,94; 52,11</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 0,0</t>
+          <t>-51,98; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 60,44</t>
+          <t>-32,56; 58,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 32,41</t>
+          <t>-17,11; 31,88</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-26,68; 25,54</t>
+          <t>-21,65; 21,69</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 57,61</t>
+          <t>-14,03; 61,81</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-61,72; 36,46</t>
+          <t>-59,27; 36,26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 53,37</t>
+          <t>-43,92; 66,03</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2204,32 +2204,32 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 46,48</t>
+          <t>-34,82; 46,04</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-37,3; 36,41</t>
+          <t>-36,47; 39,89</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-37,6; 100,0</t>
+          <t>-37,63; 100,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 34,43</t>
+          <t>-24,88; 34,53</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-21,86; 40,46</t>
+          <t>-23,79; 36,36</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 92,7</t>
+          <t>-31,08; 100,0</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 20,88</t>
+          <t>-7,78; 21,33</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 30,65</t>
+          <t>-3,51; 30,35</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 47,15</t>
+          <t>-5,67; 41,03</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 21,64</t>
+          <t>-8,2; 20,11</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 29,06</t>
+          <t>-6,48; 29,33</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 44,01</t>
+          <t>-7,64; 38,87</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 16,49</t>
+          <t>-4,42; 16,19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 23,43</t>
+          <t>-0,94; 24,29</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 32,18</t>
+          <t>0,4; 33,25</t>
         </is>
       </c>
     </row>
@@ -2511,12 +2511,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 625,71</t>
+          <t>-61,76; 629,33</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 906,0</t>
+          <t>-41,59; 775,36</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-45,6; 462,12</t>
+          <t>-47,05; 352,22</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 449,94</t>
+          <t>-46,07; 475,78</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 824,56</t>
+          <t>-62,86; 651,79</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 260,46</t>
+          <t>-31,17; 247,41</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 356,3</t>
+          <t>-11,46; 360,51</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 477,27</t>
+          <t>-9,88; 472,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Provincia-trans_camb.xlsx
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,55</t>
+          <t>0,0; 81,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,22</t>
+          <t>0,0; 70,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,34</t>
+          <t>0,0; 66,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,64</t>
+          <t>0,0; 60,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 42,56</t>
+          <t>-23,7; 42,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 60,67</t>
+          <t>-23,6; 60,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 88,39</t>
+          <t>-23,66; 88,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 40,47</t>
+          <t>-28,24; 37,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 0,0</t>
+          <t>-50,93; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 0,0</t>
+          <t>-50,76; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 30,0</t>
+          <t>-19,31; 29,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 28,37</t>
+          <t>-24,66; 31,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,85; 55,76</t>
+          <t>-19,5; 57,54</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 85,46</t>
+          <t>-43,19; 85,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-45,51; 0,0</t>
+          <t>-44,31; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,39; 59,06</t>
+          <t>-22,41; 60,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 64,22</t>
+          <t>-22,34; 57,86</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 80,79</t>
+          <t>-47,87; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 52,54</t>
+          <t>-15,59; 53,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 66,93</t>
+          <t>-10,92; 65,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 0,0</t>
+          <t>-35,67; 0,0</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 73,34</t>
+          <t>-53,38; 73,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-52,21; 43,75</t>
+          <t>-47,56; 56,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1973,12 +1973,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,77</t>
+          <t>0,0; 52,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,33</t>
+          <t>0,0; 48,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1988,32 +1988,32 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-27,94; 52,11</t>
+          <t>-29,58; 45,3</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 0,0</t>
+          <t>-59,27; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 58,35</t>
+          <t>-30,09; 58,08</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 31,88</t>
+          <t>-19,7; 33,25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 21,69</t>
+          <t>-27,76; 21,48</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,03; 61,81</t>
+          <t>-13,76; 59,95</t>
         </is>
       </c>
     </row>
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-59,27; 36,26</t>
+          <t>-58,79; 36,53</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 66,03</t>
+          <t>-42,31; 63,49</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2204,32 +2204,32 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 46,04</t>
+          <t>-36,91; 46,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 39,89</t>
+          <t>-26,47; 43,79</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-37,63; 100,0</t>
+          <t>-37,7; 100,0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 34,53</t>
+          <t>-25,79; 34,77</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-23,79; 36,36</t>
+          <t>-24,05; 39,33</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 100,0</t>
+          <t>-29,55; 100,0</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 21,33</t>
+          <t>-9,02; 19,5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 30,35</t>
+          <t>-3,29; 31,01</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 41,03</t>
+          <t>-6,28; 45,9</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 20,11</t>
+          <t>-7,6; 20,09</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 29,33</t>
+          <t>-7,92; 26,83</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 38,87</t>
+          <t>-7,43; 41,92</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 16,19</t>
+          <t>-4,8; 15,74</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 24,29</t>
+          <t>-1,65; 24,08</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,4; 33,25</t>
+          <t>-2,7; 34,41</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-61,76; 629,33</t>
+          <t>-66,93; 562,02</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 775,36</t>
+          <t>-37,11; 952,86</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1532,13</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 352,22</t>
+          <t>-46,4; 344,24</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 475,78</t>
+          <t>-56,42; 418,45</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 651,79</t>
+          <t>-49,91; 645,39</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 247,41</t>
+          <t>-34,52; 237,55</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 360,51</t>
+          <t>-15,38; 346,3</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 472,79</t>
+          <t>-27,59; 447,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18,57</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50,19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>39,8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,57</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,27</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14,55</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31,5</t>
+          <t>28,99</t>
         </is>
       </c>
     </row>
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 76,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 65,58</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,77</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,87</t>
+          <t>0,0; 62,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,5</t>
+          <t>0,0; 84,31</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-12,82</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-12,82</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,59</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,41</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26,57</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-12,82</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-12,82</t>
+          <t>26,85</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>9,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 42,74</t>
+          <t>-28,17; 40,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 60,67</t>
+          <t>-50,76; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 88,41</t>
+          <t>-50,77; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-28,24; 37,97</t>
+          <t>-23,62; 43,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 0,0</t>
+          <t>-23,66; 60,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 0,0</t>
+          <t>-23,64; 88,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-19,31; 29,8</t>
+          <t>-18,87; 29,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 31,01</t>
+          <t>-23,72; 24,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 57,54</t>
+          <t>-23,01; 59,57</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>22,2%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>72,07%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>227,52%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>58,94%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>229,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>75,69%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-28,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,82</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-28,48</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-28,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,82</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-28,48</t>
+          <t>32,63</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>7,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-71,48; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-43,25; 71,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>-71,26; 0,0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-71,48; 0,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-43,19; 85,52</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-71,48; 0,0</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 0,0</t>
+          <t>-44,47; 0,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 60,39</t>
+          <t>-29,16; 54,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 57,86</t>
+          <t>-23,4; 64,16</t>
         </is>
       </c>
     </row>
@@ -1162,39 +1162,39 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>35,48%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>51,84%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15,82</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33,9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>14,49</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,98</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-22,89</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15,82</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,9</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 100,0</t>
+          <t>0,0; 73,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-47,87; 75,06</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,16</t>
+          <t>-47,87; 77,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>-47,38; 75,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 53,19</t>
+          <t>-8,39; 56,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 65,52</t>
+          <t>-8,39; 70,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-35,67; 0,0</t>
+          <t>-38,37; 0,0</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>63,3%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>21,74%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1488,22 +1488,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>25,11</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>6,64</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>25,11</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 73,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-53,38; 74,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-47,56; 56,37</t>
+          <t>-47,58; 55,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1594,22 +1594,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>24,89%</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1709,22 +1709,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>100,0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100,0</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1815,22 +1815,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5,55</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-20,09</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8,58</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>19,76</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>19,63</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>49,12</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5,55</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-20,09</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,62</t>
+          <t>53,9</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>20,93</t>
+          <t>21,22</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,67</t>
+          <t>-30,5; 44,1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,33</t>
+          <t>-51,62; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>-34,71; 61,16</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 51,35</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 49,49</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-29,58; 45,3</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>-59,27; 0,0</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-30,09; 58,08</t>
-        </is>
-      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 33,25</t>
+          <t>-16,63; 32,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 21,48</t>
+          <t>-26,68; 25,54</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 59,95</t>
+          <t>-16,87; 58,64</t>
         </is>
       </c>
     </row>
@@ -2026,34 +2026,34 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>27,63%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>42,73%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>27,63%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>47,87%</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>59,85%</t>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>151,8%</t>
+          <t>153,95%</t>
         </is>
       </c>
     </row>
@@ -2136,34 +2136,34 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>9,88</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>0,89</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>61,87</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-1,77</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>14,2</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>9,88</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,89</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>57,46</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
           <t>5,3</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>54,72</t>
+          <t>59,13</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-58,79; 36,53</t>
+          <t>-27,22; 46,48</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 63,49</t>
+          <t>-37,3; 36,41</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-30,19; 100,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 46,12</t>
+          <t>-61,72; 36,46</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-26,47; 43,79</t>
+          <t>-44,32; 53,37</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-37,7; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 34,77</t>
+          <t>-23,89; 34,43</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 39,33</t>
+          <t>-21,86; 40,46</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-29,55; 100,0</t>
+          <t>-31,65; 92,71</t>
         </is>
       </c>
     </row>
@@ -2242,34 +2242,34 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>77,28%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>6,98%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>484,1%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-8,8%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>70,48%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>77,28%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>449,58%</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
           <t>34,15%</t>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>352,61%</t>
+          <t>381,04%</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>5,75</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>8,96</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>14,21</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>5,81</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>12,79</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>14,62</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>5,75</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>8,96</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,41</t>
+          <t>16,96</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13,95</t>
+          <t>15,4</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 19,5</t>
+          <t>-7,8; 21,64</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 31,01</t>
+          <t>-8,19; 29,06</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 45,9</t>
+          <t>-6,51; 45,83</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 20,09</t>
+          <t>-7,84; 20,88</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 26,83</t>
+          <t>-2,99; 30,65</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 41,92</t>
+          <t>-4,35; 49,43</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 15,74</t>
+          <t>-4,16; 16,49</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 24,08</t>
+          <t>-1,7; 23,43</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 34,41</t>
+          <t>-0,76; 34,46</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>46,89%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>72,98%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>115,78%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>59,82%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>131,59%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>150,45%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>72,98%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>109,29%</t>
+          <t>174,51%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>124,94%</t>
+          <t>137,97%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 562,02</t>
+          <t>-45,6; 462,12</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 952,86</t>
+          <t>-50,28; 449,94</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1532,13</t>
+          <t>-47,43; 887,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 344,24</t>
+          <t>-65,48; 625,71</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 418,45</t>
+          <t>-36,55; 906,0</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-49,91; 645,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 237,55</t>
+          <t>-29,11; 260,46</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 346,3</t>
+          <t>-17,47; 356,3</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 447,08</t>
+          <t>-6,84; 527,77</t>
         </is>
       </c>
     </row>
